--- a/public/assets/excel/employee_bank_account_details.xlsx
+++ b/public/assets/excel/employee_bank_account_details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo LOQ\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE802FB-34AA-4D8A-BBC2-35C3FE27B8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92AE9A50-6FA2-4E61-89F2-9AAC5BC00E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,17 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>Employee_id</t>
   </si>
   <si>
-    <t>Bank_id</t>
-  </si>
-  <si>
-    <t>Branch_id</t>
-  </si>
-  <si>
     <t>Account_holder_name</t>
   </si>
   <si>
@@ -104,6 +98,21 @@
   </si>
   <si>
     <t>APP000005</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First National Bank	</t>
+  </si>
+  <si>
+    <t>First National Bank</t>
+  </si>
+  <si>
+    <t>Rettaborough Branch</t>
   </si>
 </sst>
 </file>
@@ -522,137 +531,137 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2">
-        <v>1001</v>
-      </c>
-      <c r="C2">
-        <v>201</v>
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3">
-        <v>1002</v>
-      </c>
-      <c r="C3">
-        <v>202</v>
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
-        <v>1003</v>
-      </c>
-      <c r="C4">
-        <v>203</v>
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5">
-        <v>1004</v>
-      </c>
-      <c r="C5">
-        <v>204</v>
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
-        <v>1005</v>
-      </c>
-      <c r="C6">
-        <v>205</v>
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
